--- a/artfynd/A 14713-2020 artfynd.xlsx
+++ b/artfynd/A 14713-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14713-2020 artfynd.xlsx
+++ b/artfynd/A 14713-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1289,59 +1289,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69353982</v>
+        <v>2923871</v>
       </c>
       <c r="B7" t="n">
-        <v>88894</v>
+        <v>96312</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>678</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stinkande håltryffel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gautieria graveolens s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tujabeståndet, Öl</t>
+          <t>Skäftekärr 700m SO, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621408.9729000628</v>
+        <v>621373.8839547407</v>
       </c>
       <c r="R7" t="n">
-        <v>6346100.206286225</v>
+        <v>6346112.705582776</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,7 +1359,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2009-08-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1375,7 +1369,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2009-08-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1383,64 +1377,43 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>SMF veckan 2017 - Öland</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>RGC17-143</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Mikael Jeppson</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Leif Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2923871</v>
+        <v>78392176</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
+        <v>96356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1449,34 +1422,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftekärr 700m SO, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621373.8839547407</v>
+        <v>621394.3689626898</v>
       </c>
       <c r="R8" t="n">
-        <v>6346112.705582776</v>
+        <v>6346117.100588906</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1503,7 +1480,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-08-14</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1513,7 +1490,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-08-14</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1527,33 +1504,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Håkan Lernefalk, Ulrika Lernefalk, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78392176</v>
+        <v>78392173</v>
       </c>
       <c r="B9" t="n">
-        <v>96356</v>
+        <v>107997</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,21 +1539,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219677</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1667,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78392173</v>
+        <v>78392158</v>
       </c>
       <c r="B10" t="n">
-        <v>107997</v>
+        <v>98520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,21 +1656,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1784,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78392158</v>
+        <v>78392162</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
+        <v>99398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,21 +1773,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1899,123 +1872,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>78392162</v>
-      </c>
-      <c r="B12" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>221235</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vårärt</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lathyrus vernus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Skäftekärr, Öl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>621394.3689626898</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6346117.100588906</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Böda</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2019-05-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Håkan Lernefalk, Ulrika Lernefalk, Niklas Hjort</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
